--- a/tests/fixtures/reference/Test_Excell_T1_small.xlsx
+++ b/tests/fixtures/reference/Test_Excell_T1_small.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="36">
   <si>
     <t xml:space="preserve">Тест</t>
   </si>
@@ -38,6 +38,9 @@
   </si>
   <si>
     <t xml:space="preserve">№ по ред</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Анализи</t>
   </si>
   <si>
     <t xml:space="preserve">Наименование на работите</t>
@@ -179,7 +182,7 @@
     <numFmt numFmtId="165" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* \-??_-;_-@_-"/>
     <numFmt numFmtId="166" formatCode="#,##0.00"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -256,6 +259,13 @@
       <name val="Times New Roman"/>
       <family val="1"/>
       <charset val="204"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -447,7 +457,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="49">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -524,19 +534,23 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="justify" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="13" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="13" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="justify" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="14" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -556,23 +570,23 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="14" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="14" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="17" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="18" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="justify" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -588,7 +602,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -624,7 +638,7 @@
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="8" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="19" fillId="8" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -636,7 +650,7 @@
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="9" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="19" fillId="9" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -720,37 +734,37 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546a"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="e7e6e6"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4472c4"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ed7d31"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="a5a5a5"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="ffc000"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="5b9bd5"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70ad47"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563c1"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954f72"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Оffice">
@@ -889,29 +903,31 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M1048576"/>
-  <sheetFormatPr defaultColWidth="9.14453125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:N30"/>
+  <sheetFormatPr defaultColWidth="9.14453125" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="68.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="10.7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="7.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="9.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="15.86"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="7" style="1" width="9.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="9.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="31.21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="10.7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="7.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="9.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="15.86"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="8" style="1" width="9.14"/>
   </cols>
   <sheetData>
     <row r="1" s="8" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2"/>
-      <c r="B1" s="3"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="6" t="s">
+      <c r="B1" s="2"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="G1" s="7"/>
       <c r="H1" s="7"/>
+      <c r="I1" s="7"/>
     </row>
     <row r="2" s="8" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
@@ -922,8 +938,9 @@
       <c r="D2" s="9"/>
       <c r="E2" s="9"/>
       <c r="F2" s="9"/>
-      <c r="G2" s="7"/>
+      <c r="G2" s="9"/>
       <c r="H2" s="7"/>
+      <c r="I2" s="7"/>
     </row>
     <row r="3" s="8" customFormat="true" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="10" t="s">
@@ -934,8 +951,9 @@
       <c r="D3" s="10"/>
       <c r="E3" s="10"/>
       <c r="F3" s="10"/>
-      <c r="G3" s="11"/>
+      <c r="G3" s="10"/>
       <c r="H3" s="11"/>
+      <c r="I3" s="11"/>
     </row>
     <row r="4" s="8" customFormat="true" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="12"/>
@@ -944,8 +962,9 @@
       <c r="D4" s="12"/>
       <c r="E4" s="12"/>
       <c r="F4" s="12"/>
-      <c r="G4" s="11"/>
+      <c r="G4" s="12"/>
       <c r="H4" s="11"/>
+      <c r="I4" s="11"/>
     </row>
     <row r="5" s="8" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="13"/>
@@ -954,8 +973,9 @@
       <c r="D5" s="13"/>
       <c r="E5" s="13"/>
       <c r="F5" s="13"/>
-      <c r="G5" s="14"/>
-      <c r="H5" s="15"/>
+      <c r="G5" s="13"/>
+      <c r="H5" s="14"/>
+      <c r="I5" s="15"/>
     </row>
     <row r="6" s="8" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="16" t="s">
@@ -966,14 +986,15 @@
       <c r="D6" s="16"/>
       <c r="E6" s="16"/>
       <c r="F6" s="16"/>
-      <c r="G6" s="17"/>
+      <c r="G6" s="16"/>
       <c r="H6" s="17"/>
+      <c r="I6" s="17"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="18" t="s">
+      <c r="B7" s="19" t="s">
         <v>5</v>
       </c>
       <c r="C7" s="18" t="s">
@@ -988,831 +1009,396 @@
       <c r="F7" s="18" t="s">
         <v>9</v>
       </c>
+      <c r="G7" s="18" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8" s="19"/>
-      <c r="C8" s="19"/>
-      <c r="D8" s="19"/>
-      <c r="E8" s="19"/>
-      <c r="F8" s="19"/>
+      <c r="A8" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="20"/>
+      <c r="C8" s="20"/>
+      <c r="D8" s="20"/>
+      <c r="E8" s="20"/>
+      <c r="F8" s="20"/>
+      <c r="G8" s="20"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="20" t="s">
+      <c r="A9" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="21"/>
+      <c r="C9" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9" s="23"/>
+      <c r="E9" s="23"/>
+      <c r="F9" s="23"/>
+      <c r="G9" s="23"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="B10" s="24"/>
+      <c r="C10" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="D10" s="26"/>
+      <c r="E10" s="26"/>
+      <c r="F10" s="26"/>
+      <c r="G10" s="26"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="24"/>
+      <c r="B11" s="24"/>
+      <c r="C11" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="E11" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="F11" s="26"/>
+      <c r="G11" s="26"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="B12" s="24"/>
+      <c r="C12" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="D12" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="E12" s="26" t="n">
+        <v>555</v>
+      </c>
+      <c r="F12" s="26"/>
+      <c r="G12" s="26"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" s="24"/>
+      <c r="C13" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="D13" s="26"/>
+      <c r="E13" s="26"/>
+      <c r="F13" s="26"/>
+      <c r="G13" s="26"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="24"/>
+      <c r="B14" s="24"/>
+      <c r="C14" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="D14" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="E14" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="F14" s="26"/>
+      <c r="G14" s="26"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="B15" s="24"/>
+      <c r="C15" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="D15" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="E15" s="26" t="n">
         <v>11</v>
       </c>
-      <c r="B9" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" s="22"/>
-      <c r="D9" s="22"/>
-      <c r="E9" s="22"/>
-      <c r="F9" s="22"/>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="23" t="n">
+      <c r="F15" s="26"/>
+      <c r="G15" s="26"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="B16" s="29"/>
+      <c r="C16" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="D16" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="E16" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="B10" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="C10" s="25"/>
-      <c r="D10" s="25"/>
-      <c r="E10" s="25"/>
-      <c r="F10" s="25"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="23"/>
-      <c r="B11" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="C11" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="D11" s="25" t="n">
-        <v>100</v>
-      </c>
-      <c r="E11" s="25"/>
-      <c r="F11" s="25"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="23" t="n">
-        <v>2</v>
-      </c>
-      <c r="B12" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="C12" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="D12" s="25" t="n">
-        <v>555</v>
-      </c>
-      <c r="E12" s="25"/>
-      <c r="F12" s="25"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="23" t="n">
-        <v>3</v>
-      </c>
-      <c r="B13" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="C13" s="25"/>
-      <c r="D13" s="25"/>
-      <c r="E13" s="25"/>
-      <c r="F13" s="25"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="23"/>
-      <c r="B14" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="C14" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="D14" s="25" t="n">
-        <v>100</v>
-      </c>
-      <c r="E14" s="25"/>
-      <c r="F14" s="25"/>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="23" t="n">
-        <v>4</v>
-      </c>
-      <c r="B15" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="C15" s="25" t="s">
+      <c r="F16" s="29"/>
+      <c r="G16" s="29"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="B17" s="31"/>
+      <c r="C17" s="32" t="s">
+        <v>23</v>
+      </c>
+      <c r="D17" s="31" t="s">
+        <v>24</v>
+      </c>
+      <c r="E17" s="31" t="n">
+        <f aca="false">E16*6</f>
+        <v>6</v>
+      </c>
+      <c r="F17" s="31"/>
+      <c r="G17" s="31"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="B18" s="31"/>
+      <c r="C18" s="32" t="s">
+        <v>25</v>
+      </c>
+      <c r="D18" s="31" t="s">
+        <v>21</v>
+      </c>
+      <c r="E18" s="31" t="n">
+        <f aca="false">E16*1</f>
+        <v>1</v>
+      </c>
+      <c r="F18" s="31"/>
+      <c r="G18" s="31"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="24" t="n">
+        <v>6</v>
+      </c>
+      <c r="B19" s="24"/>
+      <c r="C19" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="D15" s="25" t="n">
+      <c r="D19" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="E19" s="26" t="n">
         <v>11</v>
       </c>
-      <c r="E15" s="25"/>
-      <c r="F15" s="25"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="28" t="n">
-        <v>5</v>
-      </c>
-      <c r="B16" s="29" t="s">
+      <c r="F19" s="26"/>
+      <c r="G19" s="26"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="29" t="n">
+        <v>7</v>
+      </c>
+      <c r="B20" s="29"/>
+      <c r="C20" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="E20" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" s="29"/>
+      <c r="G20" s="29"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="B21" s="31"/>
+      <c r="C21" s="32" t="s">
+        <v>23</v>
+      </c>
+      <c r="D21" s="31" t="s">
+        <v>24</v>
+      </c>
+      <c r="E21" s="31" t="n">
+        <f aca="false">E20*6</f>
+        <v>6</v>
+      </c>
+      <c r="F21" s="31"/>
+      <c r="G21" s="31"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="B22" s="31"/>
+      <c r="C22" s="32" t="s">
+        <v>25</v>
+      </c>
+      <c r="D22" s="31" t="s">
+        <v>21</v>
+      </c>
+      <c r="E22" s="31" t="n">
+        <f aca="false">E20*1</f>
+        <v>1</v>
+      </c>
+      <c r="F22" s="26"/>
+      <c r="G22" s="26"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="B23" s="26"/>
+      <c r="C23" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="D23" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="C16" s="28" t="s">
-        <v>20</v>
-      </c>
-      <c r="D16" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="E16" s="28"/>
-      <c r="F16" s="28"/>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="30" t="s">
-        <v>21</v>
-      </c>
-      <c r="B17" s="31" t="s">
-        <v>22</v>
-      </c>
-      <c r="C17" s="30" t="s">
-        <v>23</v>
-      </c>
-      <c r="D17" s="30" t="n">
-        <f aca="false">D16*6</f>
-        <v>6</v>
-      </c>
-      <c r="E17" s="30"/>
-      <c r="F17" s="30"/>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="30" t="s">
-        <v>21</v>
-      </c>
-      <c r="B18" s="31" t="s">
-        <v>24</v>
-      </c>
-      <c r="C18" s="30" t="s">
-        <v>20</v>
-      </c>
-      <c r="D18" s="30" t="n">
-        <f aca="false">D16*1</f>
-        <v>1</v>
-      </c>
-      <c r="E18" s="30"/>
-      <c r="F18" s="30"/>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="23" t="n">
-        <v>6</v>
-      </c>
-      <c r="B19" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="C19" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="D19" s="25" t="n">
+      <c r="E23" s="26" t="n">
         <v>11</v>
       </c>
-      <c r="E19" s="25"/>
-      <c r="F19" s="25"/>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="28" t="n">
-        <v>7</v>
-      </c>
-      <c r="B20" s="29" t="s">
-        <v>19</v>
-      </c>
-      <c r="C20" s="28" t="s">
-        <v>20</v>
-      </c>
-      <c r="D20" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="E20" s="28"/>
-      <c r="F20" s="28"/>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="30" t="s">
-        <v>21</v>
-      </c>
-      <c r="B21" s="31" t="s">
-        <v>22</v>
-      </c>
-      <c r="C21" s="30" t="s">
-        <v>23</v>
-      </c>
-      <c r="D21" s="30" t="n">
-        <f aca="false">D20*6</f>
-        <v>6</v>
-      </c>
-      <c r="E21" s="30"/>
-      <c r="F21" s="30"/>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="30" t="s">
-        <v>21</v>
-      </c>
-      <c r="B22" s="31" t="s">
-        <v>24</v>
-      </c>
-      <c r="C22" s="30" t="s">
-        <v>20</v>
-      </c>
-      <c r="D22" s="30" t="n">
-        <f aca="false">D20*1</f>
-        <v>1</v>
-      </c>
-      <c r="E22" s="25"/>
-      <c r="F22" s="25"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="25" t="n">
-        <v>8</v>
-      </c>
-      <c r="B23" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="C23" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="D23" s="25" t="n">
-        <v>11</v>
-      </c>
-      <c r="E23" s="25"/>
-      <c r="F23" s="25"/>
-    </row>
-    <row r="24" s="35" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="32" t="s">
-        <v>25</v>
-      </c>
-      <c r="B24" s="33" t="s">
+      <c r="F23" s="26"/>
+      <c r="G23" s="26"/>
+    </row>
+    <row r="24" s="36" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="33" t="s">
         <v>26</v>
       </c>
-      <c r="C24" s="33"/>
-      <c r="D24" s="33"/>
-      <c r="E24" s="33"/>
+      <c r="B24" s="33"/>
+      <c r="C24" s="34" t="s">
+        <v>27</v>
+      </c>
+      <c r="D24" s="34"/>
+      <c r="E24" s="34"/>
       <c r="F24" s="34"/>
-      <c r="G24" s="1"/>
+      <c r="G24" s="35"/>
       <c r="H24" s="1"/>
       <c r="I24" s="1"/>
       <c r="J24" s="1"/>
       <c r="K24" s="1"/>
       <c r="L24" s="1"/>
       <c r="M24" s="1"/>
+      <c r="N24" s="1"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="36" t="s">
-        <v>27</v>
-      </c>
-      <c r="B25" s="37" t="s">
+      <c r="A25" s="37" t="s">
         <v>28</v>
       </c>
-      <c r="C25" s="37"/>
-      <c r="D25" s="37"/>
-      <c r="E25" s="37"/>
+      <c r="B25" s="37"/>
+      <c r="C25" s="38" t="s">
+        <v>29</v>
+      </c>
+      <c r="D25" s="38"/>
+      <c r="E25" s="38"/>
       <c r="F25" s="38"/>
+      <c r="G25" s="39"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="39" t="s">
-        <v>29</v>
-      </c>
-      <c r="B26" s="40" t="s">
+      <c r="A26" s="40" t="s">
         <v>30</v>
       </c>
-      <c r="C26" s="40"/>
-      <c r="D26" s="40"/>
-      <c r="E26" s="40"/>
+      <c r="B26" s="40"/>
+      <c r="C26" s="41" t="s">
+        <v>31</v>
+      </c>
+      <c r="D26" s="41"/>
+      <c r="E26" s="41"/>
       <c r="F26" s="41"/>
-      <c r="G26" s="35"/>
-      <c r="H26" s="35"/>
-      <c r="I26" s="35"/>
-      <c r="J26" s="35"/>
-      <c r="K26" s="35"/>
-      <c r="L26" s="35"/>
-      <c r="M26" s="35"/>
+      <c r="G26" s="42"/>
+      <c r="H26" s="36"/>
+      <c r="I26" s="36"/>
+      <c r="J26" s="36"/>
+      <c r="K26" s="36"/>
+      <c r="L26" s="36"/>
+      <c r="M26" s="36"/>
+      <c r="N26" s="36"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="42" t="s">
-        <v>31</v>
-      </c>
-      <c r="B27" s="43" t="s">
+      <c r="A27" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="C27" s="43"/>
-      <c r="D27" s="43"/>
-      <c r="E27" s="43"/>
+      <c r="B27" s="43"/>
+      <c r="C27" s="44" t="s">
+        <v>33</v>
+      </c>
+      <c r="D27" s="44"/>
+      <c r="E27" s="44"/>
       <c r="F27" s="44"/>
-      <c r="G27" s="35"/>
-      <c r="H27" s="35"/>
-      <c r="I27" s="35"/>
-      <c r="J27" s="35"/>
-      <c r="K27" s="35"/>
-      <c r="L27" s="35"/>
-      <c r="M27" s="35"/>
+      <c r="G27" s="45"/>
+      <c r="H27" s="36"/>
+      <c r="I27" s="36"/>
+      <c r="J27" s="36"/>
+      <c r="K27" s="36"/>
+      <c r="L27" s="36"/>
+      <c r="M27" s="36"/>
+      <c r="N27" s="36"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="45" t="s">
-        <v>33</v>
-      </c>
-      <c r="B28" s="46" t="s">
+      <c r="A28" s="46" t="s">
         <v>34</v>
       </c>
-      <c r="C28" s="46"/>
-      <c r="D28" s="46"/>
-      <c r="E28" s="46"/>
+      <c r="B28" s="46"/>
+      <c r="C28" s="47" t="s">
+        <v>35</v>
+      </c>
+      <c r="D28" s="47"/>
+      <c r="E28" s="47"/>
       <c r="F28" s="47"/>
+      <c r="G28" s="48"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="35"/>
-      <c r="B29" s="35"/>
-      <c r="C29" s="35"/>
-      <c r="D29" s="35"/>
-      <c r="E29" s="35"/>
-      <c r="F29" s="35"/>
-      <c r="G29" s="35"/>
-      <c r="H29" s="35"/>
-      <c r="I29" s="35"/>
-      <c r="J29" s="35"/>
-      <c r="K29" s="35"/>
-      <c r="L29" s="35"/>
-      <c r="M29" s="35"/>
+      <c r="A29" s="36"/>
+      <c r="B29" s="36"/>
+      <c r="C29" s="36"/>
+      <c r="D29" s="36"/>
+      <c r="E29" s="36"/>
+      <c r="F29" s="36"/>
+      <c r="G29" s="36"/>
+      <c r="H29" s="36"/>
+      <c r="I29" s="36"/>
+      <c r="J29" s="36"/>
+      <c r="K29" s="36"/>
+      <c r="L29" s="36"/>
+      <c r="M29" s="36"/>
+      <c r="N29" s="36"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="35"/>
-      <c r="B30" s="35"/>
-      <c r="C30" s="35"/>
-      <c r="D30" s="35"/>
-      <c r="E30" s="35"/>
-      <c r="F30" s="35"/>
-      <c r="G30" s="35"/>
-      <c r="H30" s="35"/>
-      <c r="I30" s="35"/>
-      <c r="J30" s="35"/>
-      <c r="K30" s="35"/>
-      <c r="L30" s="35"/>
-      <c r="M30" s="35"/>
-    </row>
-    <row r="1048116" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048117" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048118" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048119" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048120" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048121" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048122" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048123" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048124" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048125" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048126" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048127" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048128" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048129" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048130" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048131" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048132" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048133" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048134" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048135" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048136" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048137" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048138" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048139" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048140" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048141" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048142" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048143" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048144" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048145" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048146" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048147" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048148" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048149" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048150" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048151" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048152" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048153" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048154" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048155" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048156" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048157" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048158" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048159" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048160" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048161" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048162" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048163" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048164" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048165" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048166" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048167" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048168" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048169" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048170" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048171" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048172" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048173" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048174" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048175" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048176" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048177" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048178" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048179" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048180" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048181" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048182" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048183" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048184" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048185" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048186" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048187" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048188" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048189" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048190" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048191" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048192" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048193" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048194" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048195" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048196" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048197" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048198" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048199" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048200" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048201" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048202" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048203" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048204" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048205" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048206" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048207" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048208" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048209" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048210" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048211" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048212" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048213" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048214" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048215" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048216" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048217" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048218" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048219" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048220" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048221" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048222" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048223" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048224" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048225" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048226" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048227" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048228" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048229" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048230" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048231" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048232" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048233" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048234" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048235" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048236" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048237" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048238" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048239" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048240" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048241" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048242" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048243" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048244" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048245" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048246" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048247" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048248" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048249" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048250" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048251" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048252" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048253" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048254" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048255" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048256" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048257" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048258" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048259" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048260" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048261" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048262" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048263" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048264" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048265" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048266" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048267" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048268" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048269" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048270" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048271" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048272" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048273" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048274" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048275" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048276" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048277" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048278" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048279" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048280" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048281" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048282" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048283" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048284" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048285" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048286" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048287" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048288" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048289" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048290" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048291" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048292" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048293" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048294" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048295" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048296" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048297" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048298" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048299" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048300" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048301" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048302" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048303" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048304" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048305" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048306" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048307" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048308" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048309" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048310" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048311" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048312" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048313" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048314" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048315" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048316" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048317" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048318" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048319" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048320" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048321" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048322" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048323" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048324" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048325" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048326" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048327" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048328" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048329" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048330" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048331" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048332" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048333" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048334" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048335" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048336" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048337" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048338" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048339" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048340" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048341" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048342" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048343" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048344" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048345" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048346" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048347" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048348" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048349" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048350" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048351" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048352" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048353" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048354" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048355" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048356" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048357" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048358" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048359" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048360" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048361" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048362" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048363" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048364" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048365" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048366" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048367" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048368" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048369" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048370" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048371" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048372" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048373" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048374" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048375" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048376" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048377" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048378" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048379" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048380" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048381" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048382" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048383" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048384" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048385" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048386" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048387" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048388" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048389" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048390" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048391" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048392" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048393" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048394" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048395" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048396" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048397" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048398" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048399" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048400" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048401" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048402" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048403" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048404" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048405" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048406" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048407" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048408" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048409" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048410" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048411" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048412" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048413" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048414" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048415" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048416" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048417" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048418" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048419" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048420" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048421" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048422" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048423" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048424" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048425" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048426" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048427" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048428" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048429" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048430" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048431" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048432" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048433" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048434" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048435" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048436" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048437" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048438" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048439" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048440" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048441" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048442" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048443" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048444" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048445" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048446" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048447" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048448" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048449" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048450" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048451" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048452" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048453" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048454" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048455" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048456" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048457" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048458" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048459" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048460" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048461" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048462" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048463" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048464" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048465" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048466" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048467" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048468" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048469" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048470" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048471" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048472" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048473" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048474" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048475" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048476" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048477" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048478" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048479" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048480" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048481" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048482" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048483" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048484" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048485" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048486" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048487" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048488" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048489" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048490" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048491" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048492" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048493" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048494" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048495" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048496" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048497" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048498" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048499" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048500" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048501" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048502" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048503" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048504" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048505" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048506" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048507" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048508" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048509" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048510" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048511" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048512" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048513" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048514" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048515" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048516" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048517" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048518" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048519" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048520" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048521" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048522" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048523" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048524" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048525" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048526" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048527" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048528" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048529" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048530" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048531" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048532" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048533" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048534" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048535" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048536" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048537" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048538" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048539" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048540" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048541" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048542" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048543" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048544" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048545" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048546" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048547" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048548" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048549" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048550" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048551" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048552" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048553" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048554" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048555" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048556" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048557" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048558" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048559" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048560" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048561" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048562" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048563" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048564" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048565" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048566" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048567" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048568" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048569" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048570" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048571" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048572" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048573" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048574" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048575" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048576" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+      <c r="A30" s="36"/>
+      <c r="B30" s="36"/>
+      <c r="C30" s="36"/>
+      <c r="D30" s="36"/>
+      <c r="E30" s="36"/>
+      <c r="F30" s="36"/>
+      <c r="G30" s="36"/>
+      <c r="H30" s="36"/>
+      <c r="I30" s="36"/>
+      <c r="J30" s="36"/>
+      <c r="K30" s="36"/>
+      <c r="L30" s="36"/>
+      <c r="M30" s="36"/>
+      <c r="N30" s="36"/>
+    </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="A8:G8"/>
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="A13:A14"/>
-    <mergeCell ref="B24:E24"/>
-    <mergeCell ref="B25:E25"/>
-    <mergeCell ref="B26:E26"/>
-    <mergeCell ref="B27:E27"/>
-    <mergeCell ref="B28:E28"/>
+    <mergeCell ref="C24:F24"/>
+    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="C26:F26"/>
+    <mergeCell ref="C27:F27"/>
+    <mergeCell ref="C28:F28"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
